--- a/project/outputs_xlsx_solution/test_1.2-wide.xlsx
+++ b/project/outputs_xlsx_solution/test_1.2-wide.xlsx
@@ -65,7 +65,10 @@
     <t>fld F4, 112(X0)</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
   </si>
   <si>
     <t>fld F5, 116(X0)</t>
@@ -74,10 +77,13 @@
     <t>fadd F6, F1, F2</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
   </si>
   <si>
     <t>fadd F7, F3, F4</t>
@@ -104,6 +110,9 @@
     <t>fsd F9, 136(X0)</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
     <t>fsd F10, 140(X0)</t>
   </si>
   <si>
@@ -116,13 +125,34 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -537,9 +567,6 @@
       <c r="S1">
         <v>16</v>
       </c>
-      <c r="T1">
-        <v>17</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -561,7 +588,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -581,13 +608,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -607,13 +634,13 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -632,14 +659,17 @@
       <c r="F5" t="s">
         <v>7</v>
       </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -650,22 +680,25 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" t="s">
-        <v>10</v>
-      </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -676,7 +709,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -688,13 +721,13 @@
         <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -705,7 +738,7 @@
         <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
         <v>5</v>
@@ -717,13 +750,13 @@
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -734,7 +767,7 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
         <v>5</v>
@@ -746,16 +779,16 @@
         <v>10</v>
       </c>
       <c r="K9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -766,7 +799,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
         <v>5</v>
@@ -775,19 +808,19 @@
         <v>7</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -798,7 +831,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
@@ -810,28 +843,22 @@
         <v>10</v>
       </c>
       <c r="L11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>14</v>
-      </c>
-      <c r="R11" t="s">
-        <v>14</v>
-      </c>
-      <c r="S11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -842,7 +869,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s">
         <v>5</v>
@@ -854,10 +881,10 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>13</v>
-      </c>
-      <c r="S12" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -868,7 +895,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
         <v>5</v>
@@ -877,16 +904,16 @@
         <v>7</v>
       </c>
       <c r="L13" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M13" t="s">
+        <v>10</v>
+      </c>
+      <c r="N13" t="s">
         <v>14</v>
       </c>
-      <c r="N13" t="s">
-        <v>13</v>
-      </c>
-      <c r="S13" t="s">
-        <v>13</v>
+      <c r="R13" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -897,7 +924,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J14" t="s">
         <v>5</v>
@@ -906,16 +933,16 @@
         <v>7</v>
       </c>
       <c r="M14" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="N14" t="s">
+        <v>10</v>
+      </c>
+      <c r="O14" t="s">
         <v>14</v>
       </c>
-      <c r="O14" t="s">
-        <v>13</v>
-      </c>
-      <c r="S14" t="s">
-        <v>13</v>
+      <c r="R14" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -926,7 +953,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J15" t="s">
         <v>5</v>
@@ -934,17 +961,20 @@
       <c r="K15" t="s">
         <v>7</v>
       </c>
+      <c r="M15" t="s">
+        <v>16</v>
+      </c>
       <c r="N15" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="O15" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" t="s">
         <v>14</v>
       </c>
-      <c r="P15" t="s">
-        <v>13</v>
-      </c>
       <c r="S15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -955,7 +985,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -963,19 +993,25 @@
       <c r="L16" t="s">
         <v>7</v>
       </c>
+      <c r="N16" t="s">
+        <v>16</v>
+      </c>
       <c r="O16" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>10</v>
+      </c>
+      <c r="R16" t="s">
+        <v>14</v>
       </c>
       <c r="S16" t="s">
-        <v>14</v>
-      </c>
-      <c r="T16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -983,7 +1019,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -991,31 +1027,71 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
